--- a/docentes/Cruz Alejo José Armando - Estadisticos 20231.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,33 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>MAYO</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>LUIS OMAR</t>
+  </si>
+  <si>
+    <t>CHARBEL</t>
   </si>
 </sst>
 </file>
@@ -500,19 +527,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>96.67</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -591,16 +618,19 @@
         <v>32</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>32</v>
       </c>
-      <c r="E2">
-        <v>32</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -614,16 +644,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -637,16 +670,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>96.43000000000001</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -725,16 +761,16 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>96.67</v>
+        <v>90</v>
       </c>
       <c r="H3">
         <v>8.1</v>
@@ -763,7 +799,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -773,7 +809,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -803,6 +839,75 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920167</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920169</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Cruz Alejo José Armando - Estadisticos 20231.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,31 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>MAYO</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>LUIS OMAR</t>
-  </si>
-  <si>
-    <t>CHARBEL</t>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
   </si>
 </sst>
 </file>
@@ -738,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>96.88</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -764,16 +746,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -799,7 +781,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -809,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -841,71 +823,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920001</v>
+        <v>21330051920386</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920167</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920169</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Cruz Alejo José Armando - Estadisticos 20231.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20231.xlsx
@@ -729,7 +729,7 @@
         <v>96.88</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -755,7 +755,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -781,7 +781,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Cruz Alejo José Armando - Estadisticos 20231.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20231.xlsx
@@ -729,7 +729,7 @@
         <v>96.88</v>
       </c>
       <c r="H2">
-        <v>9.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -755,7 +755,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -781,7 +781,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
